--- a/Data/EC/NIT-9013971182.xlsx
+++ b/Data/EC/NIT-9013971182.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Laura Wilches\Documents\2_ Macro Comfenalco Cartagena\Macro Aviso Incumplimiento y demás\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Operaciones\OneDrive - NIYARAKY COLOMBIA SAS OLD2\Escritorio\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2764308-F860-4D9D-B9C8-CC9EB1D056A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9961711D-7DAC-40B9-97E7-064E56473170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{867EAA08-0884-4306-B005-EAE74165DBE6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{8A24F848-F99D-4EE7-9C25-005565E23CE5}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="77">
   <si>
     <t>Tipo Doc Trabajador</t>
   </si>
@@ -68,15 +68,24 @@
     <t>CC</t>
   </si>
   <si>
+    <t>45539739</t>
+  </si>
+  <si>
+    <t>TIFFANY JULIO GALARZA</t>
+  </si>
+  <si>
+    <t>2607</t>
+  </si>
+  <si>
+    <t>2606</t>
+  </si>
+  <si>
     <t>3811345</t>
   </si>
   <si>
     <t>CRISTIAN GONZALEZ RENTERIA</t>
   </si>
   <si>
-    <t>2606</t>
-  </si>
-  <si>
     <t>2605</t>
   </si>
   <si>
@@ -191,6 +200,12 @@
     <t>ANDERSON QUINTANA OROZCO</t>
   </si>
   <si>
+    <t>1007230065</t>
+  </si>
+  <si>
+    <t>FREDY JUNIOR OLIVERA BARRIOS</t>
+  </si>
+  <si>
     <t>1047369115</t>
   </si>
   <si>
@@ -216,6 +231,12 @@
   </si>
   <si>
     <t>AMAURY TORREGLOSA CONEO</t>
+  </si>
+  <si>
+    <t>92400822</t>
+  </si>
+  <si>
+    <t>JUAN ALVAREZ CHIQUILLO</t>
   </si>
   <si>
     <t>ESTADO DE CUENTA</t>
@@ -614,22 +635,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>633769</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>55950</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>437794</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>125025</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D69191E-1405-8FFF-8359-FB619398DCFD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B784551-E347-5719-6E93-79D41BA7ED05}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -638,7 +659,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -651,7 +672,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="890944" y="236925"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -980,27 +1001,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB1C7973-BAFC-4382-BAAF-496A54B13B18}">
-  <dimension ref="B2:J132"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00C41449-D9C8-4578-B2B5-AFFBAD7645ED}">
+  <dimension ref="B2:J141"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.59765625" customWidth="1"/>
-    <col min="2" max="2" width="18.9296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="37.19921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.73046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="E2" s="29"/>
       <c r="F2" s="29"/>
@@ -1009,7 +1030,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -1020,7 +1041,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -1031,7 +1052,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -1042,10 +1063,10 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="27"/>
@@ -1058,8 +1079,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1074,15 +1095,15 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="27"/>
       <c r="E11" s="7">
-        <v>4968774</v>
+        <v>5454728</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
@@ -1090,27 +1111,27 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C13" s="5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="8" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="F13" s="5">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1130,16 +1151,16 @@
         <v>5</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.45">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1153,16 +1174,16 @@
         <v>11</v>
       </c>
       <c r="F16" s="18">
-        <v>46400</v>
+        <v>70037</v>
       </c>
       <c r="G16" s="18">
-        <v>1160000</v>
+        <v>1750905</v>
       </c>
       <c r="H16" s="19"/>
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1176,27 +1197,27 @@
         <v>12</v>
       </c>
       <c r="F17" s="18">
-        <v>46400</v>
+        <v>70037</v>
       </c>
       <c r="G17" s="18">
-        <v>1160000</v>
+        <v>1750905</v>
       </c>
       <c r="H17" s="19"/>
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F18" s="18">
         <v>46400</v>
@@ -1208,18 +1229,18 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F19" s="18">
         <v>46400</v>
@@ -1231,15 +1252,15 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E20" s="16" t="s">
         <v>15</v>
@@ -1254,15 +1275,15 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E21" s="16" t="s">
         <v>16</v>
@@ -1277,15 +1298,15 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E22" s="16" t="s">
         <v>17</v>
@@ -1300,15 +1321,15 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E23" s="16" t="s">
         <v>18</v>
@@ -1323,15 +1344,15 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E24" s="16" t="s">
         <v>19</v>
@@ -1346,15 +1367,15 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E25" s="16" t="s">
         <v>20</v>
@@ -1369,15 +1390,15 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E26" s="16" t="s">
         <v>21</v>
@@ -1392,15 +1413,15 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E27" s="16" t="s">
         <v>22</v>
@@ -1415,15 +1436,15 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E28" s="16" t="s">
         <v>23</v>
@@ -1438,15 +1459,15 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E29" s="16" t="s">
         <v>24</v>
@@ -1461,15 +1482,15 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E30" s="16" t="s">
         <v>25</v>
@@ -1484,15 +1505,15 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E31" s="16" t="s">
         <v>26</v>
@@ -1507,15 +1528,15 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E32" s="16" t="s">
         <v>27</v>
@@ -1530,15 +1551,15 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E33" s="16" t="s">
         <v>28</v>
@@ -1553,15 +1574,15 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E34" s="16" t="s">
         <v>29</v>
@@ -1576,15 +1597,15 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E35" s="16" t="s">
         <v>30</v>
@@ -1599,15 +1620,15 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E36" s="16" t="s">
         <v>31</v>
@@ -1622,15 +1643,15 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E37" s="16" t="s">
         <v>32</v>
@@ -1645,15 +1666,15 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E38" s="16" t="s">
         <v>33</v>
@@ -1668,15 +1689,15 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D39" s="17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E39" s="16" t="s">
         <v>34</v>
@@ -1691,15 +1712,15 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E40" s="16" t="s">
         <v>35</v>
@@ -1714,15 +1735,15 @@
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D41" s="17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E41" s="16" t="s">
         <v>36</v>
@@ -1737,15 +1758,15 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E42" s="16" t="s">
         <v>37</v>
@@ -1760,15 +1781,15 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D43" s="17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E43" s="16" t="s">
         <v>38</v>
@@ -1783,15 +1804,15 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D44" s="17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E44" s="16" t="s">
         <v>39</v>
@@ -1806,15 +1827,15 @@
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E45" s="16" t="s">
         <v>40</v>
@@ -1829,15 +1850,15 @@
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E46" s="16" t="s">
         <v>41</v>
@@ -1852,15 +1873,15 @@
       <c r="I46" s="19"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C47" s="16" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D47" s="17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E47" s="16" t="s">
         <v>42</v>
@@ -1875,15 +1896,15 @@
       <c r="I47" s="19"/>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E48" s="16" t="s">
         <v>43</v>
@@ -1898,15 +1919,15 @@
       <c r="I48" s="19"/>
       <c r="J48" s="20"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C49" s="16" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E49" s="16" t="s">
         <v>44</v>
@@ -1921,15 +1942,15 @@
       <c r="I49" s="19"/>
       <c r="J49" s="20"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E50" s="16" t="s">
         <v>45</v>
@@ -1944,15 +1965,15 @@
       <c r="I50" s="19"/>
       <c r="J50" s="20"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C51" s="16" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D51" s="17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E51" s="16" t="s">
         <v>46</v>
@@ -1967,21 +1988,21 @@
       <c r="I51" s="19"/>
       <c r="J51" s="20"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E52" s="16" t="s">
         <v>47</v>
       </c>
       <c r="F52" s="18">
-        <v>34027</v>
+        <v>46400</v>
       </c>
       <c r="G52" s="18">
         <v>1160000</v>
@@ -1990,44 +2011,44 @@
       <c r="I52" s="19"/>
       <c r="J52" s="20"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C53" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D53" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E53" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="D53" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="E53" s="16" t="s">
-        <v>37</v>
-      </c>
       <c r="F53" s="18">
-        <v>15600</v>
+        <v>46400</v>
       </c>
       <c r="G53" s="18">
-        <v>1300000</v>
+        <v>1160000</v>
       </c>
       <c r="H53" s="19"/>
       <c r="I53" s="19"/>
       <c r="J53" s="20"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="E54" s="16" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F54" s="18">
-        <v>1547</v>
+        <v>46400</v>
       </c>
       <c r="G54" s="18">
         <v>1160000</v>
@@ -2036,53 +2057,53 @@
       <c r="I54" s="19"/>
       <c r="J54" s="20"/>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="D55" s="17" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="E55" s="16" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="F55" s="18">
-        <v>40000</v>
+        <v>34027</v>
       </c>
       <c r="G55" s="18">
-        <v>1000000</v>
+        <v>1160000</v>
       </c>
       <c r="H55" s="19"/>
       <c r="I55" s="19"/>
       <c r="J55" s="20"/>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D56" s="17" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E56" s="16" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="F56" s="18">
-        <v>40000</v>
+        <v>15600</v>
       </c>
       <c r="G56" s="18">
-        <v>1000000</v>
+        <v>1300000</v>
       </c>
       <c r="H56" s="19"/>
       <c r="I56" s="19"/>
       <c r="J56" s="20"/>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="15" t="s">
         <v>8</v>
       </c>
@@ -2093,19 +2114,19 @@
         <v>54</v>
       </c>
       <c r="E57" s="16" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F57" s="18">
-        <v>40000</v>
+        <v>56940</v>
       </c>
       <c r="G57" s="18">
-        <v>1000000</v>
+        <v>1423500</v>
       </c>
       <c r="H57" s="19"/>
       <c r="I57" s="19"/>
       <c r="J57" s="20"/>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
         <v>8</v>
       </c>
@@ -2116,53 +2137,53 @@
         <v>54</v>
       </c>
       <c r="E58" s="16" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F58" s="18">
-        <v>40000</v>
+        <v>56940</v>
       </c>
       <c r="G58" s="18">
-        <v>1000000</v>
+        <v>1423500</v>
       </c>
       <c r="H58" s="19"/>
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C59" s="16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D59" s="17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E59" s="16" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="F59" s="18">
-        <v>40000</v>
+        <v>1547</v>
       </c>
       <c r="G59" s="18">
-        <v>1000000</v>
+        <v>1160000</v>
       </c>
       <c r="H59" s="19"/>
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C60" s="16" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D60" s="17" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E60" s="16" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F60" s="18">
         <v>40000</v>
@@ -2174,18 +2195,18 @@
       <c r="I60" s="19"/>
       <c r="J60" s="20"/>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C61" s="16" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D61" s="17" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E61" s="16" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F61" s="18">
         <v>40000</v>
@@ -2197,18 +2218,18 @@
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C62" s="16" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D62" s="17" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E62" s="16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F62" s="18">
         <v>40000</v>
@@ -2220,18 +2241,18 @@
       <c r="I62" s="19"/>
       <c r="J62" s="20"/>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C63" s="16" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D63" s="17" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E63" s="16" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F63" s="18">
         <v>40000</v>
@@ -2243,18 +2264,18 @@
       <c r="I63" s="19"/>
       <c r="J63" s="20"/>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C64" s="16" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D64" s="17" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E64" s="16" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F64" s="18">
         <v>40000</v>
@@ -2266,18 +2287,18 @@
       <c r="I64" s="19"/>
       <c r="J64" s="20"/>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C65" s="16" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D65" s="17" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E65" s="16" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F65" s="18">
         <v>40000</v>
@@ -2289,133 +2310,133 @@
       <c r="I65" s="19"/>
       <c r="J65" s="20"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C66" s="16" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D66" s="17" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E66" s="16" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F66" s="18">
-        <v>46400</v>
+        <v>40000</v>
       </c>
       <c r="G66" s="18">
-        <v>1160000</v>
+        <v>1000000</v>
       </c>
       <c r="H66" s="19"/>
       <c r="I66" s="19"/>
       <c r="J66" s="20"/>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C67" s="16" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D67" s="17" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E67" s="16" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F67" s="18">
-        <v>46400</v>
+        <v>40000</v>
       </c>
       <c r="G67" s="18">
-        <v>1160000</v>
+        <v>1000000</v>
       </c>
       <c r="H67" s="19"/>
       <c r="I67" s="19"/>
       <c r="J67" s="20"/>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C68" s="16" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D68" s="17" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E68" s="16" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F68" s="18">
-        <v>46400</v>
+        <v>40000</v>
       </c>
       <c r="G68" s="18">
-        <v>1160000</v>
+        <v>1000000</v>
       </c>
       <c r="H68" s="19"/>
       <c r="I68" s="19"/>
       <c r="J68" s="20"/>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C69" s="16" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D69" s="17" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E69" s="16" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F69" s="18">
-        <v>46400</v>
+        <v>40000</v>
       </c>
       <c r="G69" s="18">
-        <v>1160000</v>
+        <v>1000000</v>
       </c>
       <c r="H69" s="19"/>
       <c r="I69" s="19"/>
       <c r="J69" s="20"/>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C70" s="16" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D70" s="17" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E70" s="16" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F70" s="18">
-        <v>46400</v>
+        <v>40000</v>
       </c>
       <c r="G70" s="18">
-        <v>1160000</v>
+        <v>1000000</v>
       </c>
       <c r="H70" s="19"/>
       <c r="I70" s="19"/>
       <c r="J70" s="20"/>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C71" s="16" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D71" s="17" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E71" s="16" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F71" s="18">
         <v>46400</v>
@@ -2427,18 +2448,18 @@
       <c r="I71" s="19"/>
       <c r="J71" s="20"/>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B72" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C72" s="16" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D72" s="17" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E72" s="16" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F72" s="18">
         <v>46400</v>
@@ -2450,18 +2471,18 @@
       <c r="I72" s="19"/>
       <c r="J72" s="20"/>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C73" s="16" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D73" s="17" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E73" s="16" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F73" s="18">
         <v>46400</v>
@@ -2473,18 +2494,18 @@
       <c r="I73" s="19"/>
       <c r="J73" s="20"/>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C74" s="16" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D74" s="17" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E74" s="16" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F74" s="18">
         <v>46400</v>
@@ -2496,18 +2517,18 @@
       <c r="I74" s="19"/>
       <c r="J74" s="20"/>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C75" s="16" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D75" s="17" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E75" s="16" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F75" s="18">
         <v>46400</v>
@@ -2519,18 +2540,18 @@
       <c r="I75" s="19"/>
       <c r="J75" s="20"/>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C76" s="16" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D76" s="17" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E76" s="16" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F76" s="18">
         <v>46400</v>
@@ -2542,18 +2563,18 @@
       <c r="I76" s="19"/>
       <c r="J76" s="20"/>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C77" s="16" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D77" s="17" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E77" s="16" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F77" s="18">
         <v>46400</v>
@@ -2565,18 +2586,18 @@
       <c r="I77" s="19"/>
       <c r="J77" s="20"/>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B78" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C78" s="16" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D78" s="17" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E78" s="16" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F78" s="18">
         <v>46400</v>
@@ -2588,18 +2609,18 @@
       <c r="I78" s="19"/>
       <c r="J78" s="20"/>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B79" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C79" s="16" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D79" s="17" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E79" s="16" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F79" s="18">
         <v>46400</v>
@@ -2611,18 +2632,18 @@
       <c r="I79" s="19"/>
       <c r="J79" s="20"/>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B80" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C80" s="16" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D80" s="17" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E80" s="16" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F80" s="18">
         <v>46400</v>
@@ -2634,18 +2655,18 @@
       <c r="I80" s="19"/>
       <c r="J80" s="20"/>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B81" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C81" s="16" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D81" s="17" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E81" s="16" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F81" s="18">
         <v>46400</v>
@@ -2657,18 +2678,18 @@
       <c r="I81" s="19"/>
       <c r="J81" s="20"/>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C82" s="16" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D82" s="17" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E82" s="16" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F82" s="18">
         <v>46400</v>
@@ -2680,18 +2701,18 @@
       <c r="I82" s="19"/>
       <c r="J82" s="20"/>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C83" s="16" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D83" s="17" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E83" s="16" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F83" s="18">
         <v>46400</v>
@@ -2703,18 +2724,18 @@
       <c r="I83" s="19"/>
       <c r="J83" s="20"/>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B84" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C84" s="16" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D84" s="17" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E84" s="16" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F84" s="18">
         <v>46400</v>
@@ -2726,18 +2747,18 @@
       <c r="I84" s="19"/>
       <c r="J84" s="20"/>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B85" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C85" s="16" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D85" s="17" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E85" s="16" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F85" s="18">
         <v>46400</v>
@@ -2749,18 +2770,18 @@
       <c r="I85" s="19"/>
       <c r="J85" s="20"/>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B86" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C86" s="16" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D86" s="17" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E86" s="16" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F86" s="18">
         <v>46400</v>
@@ -2772,18 +2793,18 @@
       <c r="I86" s="19"/>
       <c r="J86" s="20"/>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B87" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C87" s="16" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D87" s="17" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E87" s="16" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F87" s="18">
         <v>46400</v>
@@ -2795,18 +2816,18 @@
       <c r="I87" s="19"/>
       <c r="J87" s="20"/>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B88" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C88" s="16" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D88" s="17" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E88" s="16" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F88" s="18">
         <v>46400</v>
@@ -2818,18 +2839,18 @@
       <c r="I88" s="19"/>
       <c r="J88" s="20"/>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B89" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C89" s="16" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D89" s="17" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E89" s="16" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F89" s="18">
         <v>46400</v>
@@ -2841,18 +2862,18 @@
       <c r="I89" s="19"/>
       <c r="J89" s="20"/>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B90" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C90" s="16" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D90" s="17" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E90" s="16" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F90" s="18">
         <v>46400</v>
@@ -2864,18 +2885,18 @@
       <c r="I90" s="19"/>
       <c r="J90" s="20"/>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B91" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C91" s="16" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D91" s="17" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E91" s="16" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F91" s="18">
         <v>46400</v>
@@ -2887,18 +2908,18 @@
       <c r="I91" s="19"/>
       <c r="J91" s="20"/>
     </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B92" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C92" s="16" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D92" s="17" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E92" s="16" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F92" s="18">
         <v>46400</v>
@@ -2910,18 +2931,18 @@
       <c r="I92" s="19"/>
       <c r="J92" s="20"/>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B93" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C93" s="16" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D93" s="17" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E93" s="16" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F93" s="18">
         <v>46400</v>
@@ -2933,18 +2954,18 @@
       <c r="I93" s="19"/>
       <c r="J93" s="20"/>
     </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B94" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C94" s="16" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D94" s="17" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E94" s="16" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F94" s="18">
         <v>46400</v>
@@ -2956,18 +2977,18 @@
       <c r="I94" s="19"/>
       <c r="J94" s="20"/>
     </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B95" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C95" s="16" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D95" s="17" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E95" s="16" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F95" s="18">
         <v>46400</v>
@@ -2979,18 +3000,18 @@
       <c r="I95" s="19"/>
       <c r="J95" s="20"/>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B96" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C96" s="16" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D96" s="17" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E96" s="16" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F96" s="18">
         <v>46400</v>
@@ -3002,18 +3023,18 @@
       <c r="I96" s="19"/>
       <c r="J96" s="20"/>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B97" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C97" s="16" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D97" s="17" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E97" s="16" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F97" s="18">
         <v>46400</v>
@@ -3025,18 +3046,18 @@
       <c r="I97" s="19"/>
       <c r="J97" s="20"/>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B98" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C98" s="16" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D98" s="17" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E98" s="16" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F98" s="18">
         <v>46400</v>
@@ -3048,18 +3069,18 @@
       <c r="I98" s="19"/>
       <c r="J98" s="20"/>
     </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B99" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C99" s="16" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D99" s="17" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E99" s="16" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F99" s="18">
         <v>46400</v>
@@ -3071,21 +3092,21 @@
       <c r="I99" s="19"/>
       <c r="J99" s="20"/>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B100" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C100" s="16" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D100" s="17" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E100" s="16" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F100" s="18">
-        <v>23200</v>
+        <v>46400</v>
       </c>
       <c r="G100" s="18">
         <v>1160000</v>
@@ -3094,18 +3115,18 @@
       <c r="I100" s="19"/>
       <c r="J100" s="20"/>
     </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B101" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C101" s="16" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D101" s="17" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E101" s="16" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="F101" s="18">
         <v>46400</v>
@@ -3117,18 +3138,18 @@
       <c r="I101" s="19"/>
       <c r="J101" s="20"/>
     </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="102" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B102" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C102" s="16" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D102" s="17" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E102" s="16" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="F102" s="18">
         <v>46400</v>
@@ -3140,18 +3161,18 @@
       <c r="I102" s="19"/>
       <c r="J102" s="20"/>
     </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B103" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C103" s="16" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D103" s="17" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E103" s="16" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="F103" s="18">
         <v>46400</v>
@@ -3163,18 +3184,18 @@
       <c r="I103" s="19"/>
       <c r="J103" s="20"/>
     </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="104" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B104" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C104" s="16" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D104" s="17" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E104" s="16" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="F104" s="18">
         <v>46400</v>
@@ -3186,18 +3207,18 @@
       <c r="I104" s="19"/>
       <c r="J104" s="20"/>
     </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="105" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B105" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C105" s="16" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D105" s="17" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E105" s="16" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F105" s="18">
         <v>46400</v>
@@ -3209,21 +3230,21 @@
       <c r="I105" s="19"/>
       <c r="J105" s="20"/>
     </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="106" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B106" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C106" s="16" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D106" s="17" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E106" s="16" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="F106" s="18">
-        <v>46400</v>
+        <v>23200</v>
       </c>
       <c r="G106" s="18">
         <v>1160000</v>
@@ -3232,18 +3253,18 @@
       <c r="I106" s="19"/>
       <c r="J106" s="20"/>
     </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="107" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B107" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C107" s="16" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D107" s="17" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E107" s="16" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F107" s="18">
         <v>46400</v>
@@ -3255,18 +3276,18 @@
       <c r="I107" s="19"/>
       <c r="J107" s="20"/>
     </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="108" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B108" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C108" s="16" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D108" s="17" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E108" s="16" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F108" s="18">
         <v>46400</v>
@@ -3278,18 +3299,18 @@
       <c r="I108" s="19"/>
       <c r="J108" s="20"/>
     </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="109" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B109" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C109" s="16" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D109" s="17" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E109" s="16" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F109" s="18">
         <v>46400</v>
@@ -3301,18 +3322,18 @@
       <c r="I109" s="19"/>
       <c r="J109" s="20"/>
     </row>
-    <row r="110" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="110" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B110" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C110" s="16" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D110" s="17" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E110" s="16" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F110" s="18">
         <v>46400</v>
@@ -3324,18 +3345,18 @@
       <c r="I110" s="19"/>
       <c r="J110" s="20"/>
     </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="111" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B111" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C111" s="16" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D111" s="17" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E111" s="16" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F111" s="18">
         <v>46400</v>
@@ -3347,18 +3368,18 @@
       <c r="I111" s="19"/>
       <c r="J111" s="20"/>
     </row>
-    <row r="112" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="112" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B112" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C112" s="16" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D112" s="17" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E112" s="16" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F112" s="18">
         <v>46400</v>
@@ -3370,18 +3391,18 @@
       <c r="I112" s="19"/>
       <c r="J112" s="20"/>
     </row>
-    <row r="113" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="113" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B113" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C113" s="16" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D113" s="17" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E113" s="16" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F113" s="18">
         <v>46400</v>
@@ -3393,18 +3414,18 @@
       <c r="I113" s="19"/>
       <c r="J113" s="20"/>
     </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="114" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B114" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C114" s="16" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D114" s="17" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E114" s="16" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F114" s="18">
         <v>46400</v>
@@ -3416,18 +3437,18 @@
       <c r="I114" s="19"/>
       <c r="J114" s="20"/>
     </row>
-    <row r="115" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="115" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B115" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C115" s="16" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D115" s="17" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E115" s="16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F115" s="18">
         <v>46400</v>
@@ -3439,18 +3460,18 @@
       <c r="I115" s="19"/>
       <c r="J115" s="20"/>
     </row>
-    <row r="116" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="116" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B116" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C116" s="16" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D116" s="17" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E116" s="16" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F116" s="18">
         <v>46400</v>
@@ -3462,18 +3483,18 @@
       <c r="I116" s="19"/>
       <c r="J116" s="20"/>
     </row>
-    <row r="117" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="117" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B117" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C117" s="16" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D117" s="17" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E117" s="16" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F117" s="18">
         <v>46400</v>
@@ -3485,18 +3506,18 @@
       <c r="I117" s="19"/>
       <c r="J117" s="20"/>
     </row>
-    <row r="118" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="118" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B118" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C118" s="16" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D118" s="17" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E118" s="16" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F118" s="18">
         <v>46400</v>
@@ -3508,18 +3529,18 @@
       <c r="I118" s="19"/>
       <c r="J118" s="20"/>
     </row>
-    <row r="119" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="119" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B119" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C119" s="16" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D119" s="17" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E119" s="16" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F119" s="18">
         <v>46400</v>
@@ -3531,18 +3552,18 @@
       <c r="I119" s="19"/>
       <c r="J119" s="20"/>
     </row>
-    <row r="120" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="120" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B120" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C120" s="16" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D120" s="17" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E120" s="16" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F120" s="18">
         <v>46400</v>
@@ -3554,18 +3575,18 @@
       <c r="I120" s="19"/>
       <c r="J120" s="20"/>
     </row>
-    <row r="121" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="121" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B121" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C121" s="16" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D121" s="17" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E121" s="16" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F121" s="18">
         <v>46400</v>
@@ -3577,18 +3598,18 @@
       <c r="I121" s="19"/>
       <c r="J121" s="20"/>
     </row>
-    <row r="122" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="122" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B122" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C122" s="16" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D122" s="17" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E122" s="16" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F122" s="18">
         <v>46400</v>
@@ -3600,18 +3621,18 @@
       <c r="I122" s="19"/>
       <c r="J122" s="20"/>
     </row>
-    <row r="123" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="123" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B123" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C123" s="16" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D123" s="17" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E123" s="16" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F123" s="18">
         <v>46400</v>
@@ -3623,18 +3644,18 @@
       <c r="I123" s="19"/>
       <c r="J123" s="20"/>
     </row>
-    <row r="124" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="124" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B124" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C124" s="16" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D124" s="17" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E124" s="16" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F124" s="18">
         <v>46400</v>
@@ -3646,18 +3667,18 @@
       <c r="I124" s="19"/>
       <c r="J124" s="20"/>
     </row>
-    <row r="125" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="125" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B125" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C125" s="16" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D125" s="17" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E125" s="16" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F125" s="18">
         <v>46400</v>
@@ -3669,57 +3690,264 @@
       <c r="I125" s="19"/>
       <c r="J125" s="20"/>
     </row>
-    <row r="126" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B126" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C126" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="D126" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="E126" s="22" t="s">
+    <row r="126" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B126" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C126" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="D126" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="E126" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="F126" s="18">
+        <v>46400</v>
+      </c>
+      <c r="G126" s="18">
+        <v>1160000</v>
+      </c>
+      <c r="H126" s="19"/>
+      <c r="I126" s="19"/>
+      <c r="J126" s="20"/>
+    </row>
+    <row r="127" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B127" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C127" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="D127" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="E127" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F127" s="18">
+        <v>46400</v>
+      </c>
+      <c r="G127" s="18">
+        <v>1160000</v>
+      </c>
+      <c r="H127" s="19"/>
+      <c r="I127" s="19"/>
+      <c r="J127" s="20"/>
+    </row>
+    <row r="128" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B128" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C128" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="D128" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="E128" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F128" s="18">
+        <v>46400</v>
+      </c>
+      <c r="G128" s="18">
+        <v>1160000</v>
+      </c>
+      <c r="H128" s="19"/>
+      <c r="I128" s="19"/>
+      <c r="J128" s="20"/>
+    </row>
+    <row r="129" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B129" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C129" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="D129" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="E129" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F129" s="18">
+        <v>46400</v>
+      </c>
+      <c r="G129" s="18">
+        <v>1160000</v>
+      </c>
+      <c r="H129" s="19"/>
+      <c r="I129" s="19"/>
+      <c r="J129" s="20"/>
+    </row>
+    <row r="130" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B130" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C130" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="D130" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="E130" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="F126" s="24">
-        <v>46400</v>
-      </c>
-      <c r="G126" s="24">
-        <v>1160000</v>
-      </c>
-      <c r="H126" s="25"/>
-      <c r="I126" s="25"/>
-      <c r="J126" s="26"/>
-    </row>
-    <row r="131" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B131" s="32" t="s">
-        <v>68</v>
-      </c>
-      <c r="C131" s="32"/>
-      <c r="H131" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="I131" s="1"/>
-      <c r="J131" s="1"/>
-    </row>
-    <row r="132" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B132" s="32" t="s">
-        <v>67</v>
-      </c>
-      <c r="C132" s="32"/>
-      <c r="H132" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I132" s="1"/>
-      <c r="J132" s="1"/>
+      <c r="F130" s="18">
+        <v>46400</v>
+      </c>
+      <c r="G130" s="18">
+        <v>1160000</v>
+      </c>
+      <c r="H130" s="19"/>
+      <c r="I130" s="19"/>
+      <c r="J130" s="20"/>
+    </row>
+    <row r="131" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B131" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C131" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="D131" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="E131" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="F131" s="18">
+        <v>46400</v>
+      </c>
+      <c r="G131" s="18">
+        <v>1160000</v>
+      </c>
+      <c r="H131" s="19"/>
+      <c r="I131" s="19"/>
+      <c r="J131" s="20"/>
+    </row>
+    <row r="132" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B132" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C132" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="D132" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="E132" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="F132" s="18">
+        <v>46400</v>
+      </c>
+      <c r="G132" s="18">
+        <v>1160000</v>
+      </c>
+      <c r="H132" s="19"/>
+      <c r="I132" s="19"/>
+      <c r="J132" s="20"/>
+    </row>
+    <row r="133" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B133" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C133" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="D133" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="E133" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="F133" s="18">
+        <v>46400</v>
+      </c>
+      <c r="G133" s="18">
+        <v>1160000</v>
+      </c>
+      <c r="H133" s="19"/>
+      <c r="I133" s="19"/>
+      <c r="J133" s="20"/>
+    </row>
+    <row r="134" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B134" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C134" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D134" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E134" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F134" s="18">
+        <v>46400</v>
+      </c>
+      <c r="G134" s="18">
+        <v>1160000</v>
+      </c>
+      <c r="H134" s="19"/>
+      <c r="I134" s="19"/>
+      <c r="J134" s="20"/>
+    </row>
+    <row r="135" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B135" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C135" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="D135" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="E135" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F135" s="24">
+        <v>46400</v>
+      </c>
+      <c r="G135" s="24">
+        <v>1160000</v>
+      </c>
+      <c r="H135" s="25"/>
+      <c r="I135" s="25"/>
+      <c r="J135" s="26"/>
+    </row>
+    <row r="140" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B140" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="C140" s="32"/>
+      <c r="H140" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I140" s="1"/>
+      <c r="J140" s="1"/>
+    </row>
+    <row r="141" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B141" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="C141" s="32"/>
+      <c r="H141" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I141" s="1"/>
+      <c r="J141" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="H132:J132"/>
-    <mergeCell ref="H131:J131"/>
+    <mergeCell ref="B141:C141"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="H141:J141"/>
+    <mergeCell ref="H140:J140"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="D2:J5"/>
